--- a/分店财务报表模板.xlsx
+++ b/分店财务报表模板.xlsx
@@ -7,8 +7,11 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="19420" windowHeight="11020"/>
   </bookViews>
   <sheets>
-    <sheet name="三江店报表" sheetId="1" r:id="rId1"/>
+    <sheet name="sheet" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet!$A$2:$N$10</definedName>
+  </definedNames>
   <calcPr calcId="114210"/>
 </workbook>
 </file>
@@ -47,10 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>三江店</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>1月</t>
   </si>
@@ -279,13 +279,15 @@
     <t>分红</t>
   </si>
   <si>
-    <t>总分红（往年分红60万）</t>
-  </si>
-  <si>
-    <t>投资250万</t>
-  </si>
-  <si>
     <t>银行余额</t>
+  </si>
+  <si>
+    <t>投资</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>总分红（往年分红万）</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -372,25 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="13"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="31"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="47"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="51"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="13"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,7 +553,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -596,76 +598,76 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="7" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="7" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -677,35 +679,35 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1210,52 +1212,50 @@
       <c r="A1" s="6"/>
     </row>
     <row r="2" spans="1:14" ht="20" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="M2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="N2" s="9" t="s">
         <v>12</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="20" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -1273,7 +1273,7 @@
     </row>
     <row r="4" spans="1:14" ht="20" customHeight="1">
       <c r="A4" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="5" spans="1:14" ht="20" customHeight="1">
       <c r="A5" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
@@ -1309,7 +1309,7 @@
     </row>
     <row r="6" spans="1:14" ht="20" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="7" spans="1:14" ht="20" customHeight="1">
       <c r="A7" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -1345,7 +1345,7 @@
     </row>
     <row r="8" spans="1:14" ht="20" customHeight="1">
       <c r="A8" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="9" spans="1:14" ht="20" customHeight="1">
       <c r="A9" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="10" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A10" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -1431,7 +1431,7 @@
     </row>
     <row r="13" spans="1:14" ht="20" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="14" spans="1:14" ht="20" customHeight="1">
       <c r="A14" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="15" spans="1:14" ht="20" customHeight="1">
       <c r="A15" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -1485,7 +1485,7 @@
     </row>
     <row r="16" spans="1:14" ht="20" customHeight="1">
       <c r="A16" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="17" spans="1:15" ht="20" customHeight="1">
       <c r="A17" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="18" spans="1:15" s="2" customFormat="1" ht="20" customHeight="1">
       <c r="A18" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="23"/>
       <c r="C18" s="23"/>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="19" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A19" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="26"/>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="21" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A21" s="25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="26"/>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="23" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A23" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="26"/>
       <c r="C23" s="26"/>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="25" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A25" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="26"/>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="27" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A27" s="29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="29" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A29" s="29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="31" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A31" s="29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" s="26"/>
       <c r="C31" s="26"/>
@@ -1792,7 +1792,7 @@
     </row>
     <row r="33" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A33" s="29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B33" s="26"/>
       <c r="C33" s="26"/>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="35" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A35" s="29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" s="26"/>
       <c r="C35" s="26"/>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="37" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A37" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="26"/>
       <c r="C37" s="26"/>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="39" spans="1:15" s="2" customFormat="1" ht="20" customHeight="1">
       <c r="A39" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
@@ -1919,7 +1919,7 @@
     </row>
     <row r="40" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A40" s="29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="26"/>
       <c r="C40" s="26"/>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="42" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A42" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="26"/>
       <c r="C42" s="26"/>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="44" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A44" s="29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="26"/>
       <c r="C44" s="26"/>
@@ -2027,7 +2027,7 @@
     </row>
     <row r="46" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A46" s="29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B46" s="26"/>
       <c r="C46" s="26"/>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="48" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A48" s="29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="26"/>
       <c r="C48" s="26"/>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="50" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A50" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B50" s="26"/>
       <c r="C50" s="26"/>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="52" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A52" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B52" s="26"/>
       <c r="C52" s="26"/>
@@ -2171,13 +2171,13 @@
     </row>
     <row r="54" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A54" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B54" s="26"/>
       <c r="C54" s="26"/>
       <c r="D54" s="26"/>
       <c r="E54" s="26"/>
-      <c r="F54" s="52"/>
+      <c r="F54" s="51"/>
       <c r="G54" s="26"/>
       <c r="H54" s="26"/>
       <c r="I54" s="26"/>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="56" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A56" s="29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" s="26"/>
       <c r="C56" s="26"/>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="58" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A58" s="29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B58" s="26"/>
       <c r="C58" s="26"/>
@@ -2279,7 +2279,7 @@
     </row>
     <row r="60" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A60" s="29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B60" s="26"/>
       <c r="C60" s="26"/>
@@ -2315,7 +2315,7 @@
     </row>
     <row r="62" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A62" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B62" s="31"/>
       <c r="C62" s="31"/>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="64" spans="1:15" s="2" customFormat="1" ht="20" customHeight="1">
       <c r="A64" s="22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B64" s="23"/>
       <c r="C64" s="23"/>
@@ -2367,12 +2367,12 @@
       <c r="M64" s="23"/>
       <c r="N64" s="23"/>
       <c r="O64" s="35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A65" s="29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B65" s="26"/>
       <c r="C65" s="26"/>
@@ -2405,12 +2405,12 @@
       <c r="M66" s="28"/>
       <c r="N66" s="28"/>
       <c r="O66" s="35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A67" s="36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B67" s="37"/>
       <c r="C67" s="37"/>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="68" spans="1:15" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A68" s="38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B68" s="39"/>
       <c r="C68" s="39"/>
@@ -2445,12 +2445,12 @@
       <c r="M68" s="39"/>
       <c r="N68" s="39"/>
       <c r="O68" s="35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="20" customHeight="1">
       <c r="A69" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B69" s="41"/>
       <c r="C69" s="41"/>
@@ -2467,66 +2467,61 @@
       <c r="N69" s="42"/>
     </row>
     <row r="70" spans="1:15" ht="20" customHeight="1">
-      <c r="A70" s="43" t="s">
+      <c r="A70" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="B70" s="43"/>
+      <c r="C70" s="43"/>
+      <c r="D70" s="43"/>
+      <c r="E70" s="43"/>
+      <c r="F70" s="43"/>
+      <c r="G70" s="43"/>
+      <c r="H70" s="43"/>
+      <c r="I70" s="43"/>
+      <c r="J70" s="43"/>
+      <c r="K70" s="43"/>
+      <c r="L70" s="43"/>
+      <c r="M70" s="43"/>
+      <c r="N70" s="44"/>
+    </row>
+    <row r="71" spans="1:15" ht="20" customHeight="1">
+      <c r="A71" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="B70" s="44"/>
-      <c r="C70" s="44"/>
-      <c r="D70" s="44"/>
-      <c r="E70" s="44"/>
-      <c r="F70" s="44"/>
-      <c r="G70" s="44"/>
-      <c r="H70" s="44"/>
-      <c r="I70" s="44"/>
-      <c r="J70" s="44"/>
-      <c r="K70" s="44"/>
-      <c r="L70" s="44"/>
-      <c r="M70" s="44"/>
-      <c r="N70" s="45"/>
-    </row>
-    <row r="71" spans="1:15" ht="20" customHeight="1">
-      <c r="A71" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="47"/>
-      <c r="J71" s="47"/>
-      <c r="K71" s="47"/>
-      <c r="L71" s="47"/>
-      <c r="M71" s="47"/>
-      <c r="N71" s="48"/>
+      <c r="B71" s="46"/>
+      <c r="C71" s="46"/>
+      <c r="D71" s="46"/>
+      <c r="E71" s="46"/>
+      <c r="F71" s="46"/>
+      <c r="G71" s="46"/>
+      <c r="H71" s="46"/>
+      <c r="I71" s="46"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="46"/>
+      <c r="L71" s="46"/>
+      <c r="M71" s="46"/>
+      <c r="N71" s="47"/>
     </row>
     <row r="72" spans="1:15" ht="20" customHeight="1">
-      <c r="A72" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B72" s="50"/>
-      <c r="C72" s="50"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="50"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="50"/>
-      <c r="H72" s="50"/>
-      <c r="I72" s="51"/>
-      <c r="J72" s="51"/>
-      <c r="K72" s="51"/>
-      <c r="L72" s="51"/>
-      <c r="M72" s="51"/>
-      <c r="N72" s="50"/>
+      <c r="A72" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="B72" s="49"/>
+      <c r="C72" s="49"/>
+      <c r="D72" s="49"/>
+      <c r="E72" s="49"/>
+      <c r="F72" s="49"/>
+      <c r="G72" s="49"/>
+      <c r="H72" s="49"/>
+      <c r="I72" s="50"/>
+      <c r="J72" s="50"/>
+      <c r="K72" s="50"/>
+      <c r="L72" s="50"/>
+      <c r="M72" s="50"/>
+      <c r="N72" s="49"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2">
-      <formula1>"广场店,保利店1,保利店2,柳南店,柳工店,步步高店,柳石店,京东店,五星店,玉林店,吾悦店,城中万达店,鹅山店,三江店"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.55069444444444404" right="0.35416666666666702" top="0.23611111111111099" bottom="0.23611111111111099" header="0.23611111111111099" footer="0.118055555555556"/>
   <pageSetup paperSize="9" scale="57" fitToWidth="0" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
